--- a/backend/models/tabpfn_adasyn/leaderboard.xlsx
+++ b/backend/models/tabpfn_adasyn/leaderboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,26 @@
           <t>fit_order</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,22 +533,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.250342845916748</v>
+        <v>0.2571749687194824</v>
       </c>
       <c r="F2" t="n">
-        <v>1.726164817810059</v>
+        <v>1.757252931594849</v>
       </c>
       <c r="G2" t="n">
-        <v>2.735604047775269</v>
+        <v>2.779919624328613</v>
       </c>
       <c r="H2" t="n">
-        <v>0.250342845916748</v>
+        <v>0.2571749687194824</v>
       </c>
       <c r="I2" t="n">
-        <v>1.726164817810059</v>
+        <v>1.757252931594849</v>
       </c>
       <c r="J2" t="n">
-        <v>2.735604047775269</v>
+        <v>2.779919624328613</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -537,6 +557,18 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -558,22 +590,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2511730194091797</v>
+        <v>0.2580375671386719</v>
       </c>
       <c r="F3" t="n">
-        <v>1.726414203643799</v>
+        <v>1.757501363754272</v>
       </c>
       <c r="G3" t="n">
-        <v>2.736890554428101</v>
+        <v>2.781118869781494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008301734924316406</v>
+        <v>0.0008625984191894531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002493858337402344</v>
+        <v>0.0002484321594238281</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001286506652832031</v>
+        <v>0.001199245452880859</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -583,6 +615,18 @@
       </c>
       <c r="M3" t="n">
         <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -603,22 +647,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4900996685028076</v>
+        <v>0.5155699253082275</v>
       </c>
       <c r="F4" t="n">
-        <v>3.473410844802856</v>
+        <v>3.525348901748657</v>
       </c>
       <c r="G4" t="n">
-        <v>5.524394989013672</v>
+        <v>5.593779802322388</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2397568225860596</v>
+        <v>0.2583949565887451</v>
       </c>
       <c r="I4" t="n">
-        <v>1.747246026992798</v>
+        <v>1.768095970153809</v>
       </c>
       <c r="J4" t="n">
-        <v>2.788790941238403</v>
+        <v>2.813860177993774</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -628,6 +672,18 @@
       </c>
       <c r="M4" t="n">
         <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -648,22 +704,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4908788204193115</v>
+        <v>0.5164122581481934</v>
       </c>
       <c r="F5" t="n">
-        <v>3.473641633987427</v>
+        <v>3.525591611862183</v>
       </c>
       <c r="G5" t="n">
-        <v>5.525526285171509</v>
+        <v>5.594977855682373</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007791519165039062</v>
+        <v>0.0008423328399658203</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002307891845703125</v>
+        <v>0.0002427101135253906</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001131296157836914</v>
+        <v>0.001198053359985352</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -673,6 +729,18 @@
       </c>
       <c r="M5" t="n">
         <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
